--- a/naver-place-crawler/results_health/창원_헬스장.xlsx
+++ b/naver-place-crawler/results_health/창원_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="43" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>캡틴짐 헬스&amp;PT 24시 마산월영점</t>
+          <t>빅스짐 중동점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>captaingym_m@naver.com</t>
+          <t>bhy0565@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1432-9683</t>
+          <t>0507-1349-8501</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경상남도 창원시 마산합포구 해안대로 91 3층 캡틴짐</t>
+          <t>경남 창원시 의창구 중동중앙로 47 어반브릭스 오피스타워 21층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/captaingym_wolyeong?igsh=a2x0NWNmcGNxdTAy</t>
+          <t>https://www.instagram.com/bigsgym_jungdong/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wce7fp</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>823</v>
+        <v>1318</v>
       </c>
       <c r="Q2" t="n">
-        <v>662</v>
+        <v>1580</v>
       </c>
       <c r="R2" t="n">
-        <v>1485</v>
+        <v>2898</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,56 +640,56 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1454603225</t>
+          <t>1259062125</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1454603225</t>
+          <t>https://m.place.naver.com/place/1259062125</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>몸가짐피트니스 상남점 헬스 PT</t>
+          <t>메인핏 양덕2호점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dgrdgrdgrdgr@naver.com</t>
+          <t>mainfit2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1441-5059</t>
+          <t>0507-1438-1778</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경상남도 창원시 성산구 마디미서로 26 한독빌딩 7층 몸가짐 피트니스</t>
+          <t>경남 창원시 마산회원구 봉양로 41 동원엠디스타 9,10층 3,4호 메인핏</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dgrdgrdgrdgr</t>
+          <t>https://map.naver.com/p/entry/place/1182203243?c=15.00,0,0,0,dh&amp;placePath=/ticket</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xh92</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>549</v>
+        <v>388</v>
       </c>
       <c r="Q3" t="n">
-        <v>938</v>
+        <v>554</v>
       </c>
       <c r="R3" t="n">
-        <v>1487</v>
+        <v>942</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,56 +738,56 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1423723739</t>
+          <t>1182203243</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1423723739</t>
+          <t>https://m.place.naver.com/place/1182203243</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피트니스055 상남점 헬스&amp;PT</t>
+          <t>캡틴짐 헬스&amp;PT 24시 마산월영점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fitness055_sangnam@naver.com</t>
+          <t>captaingym_m@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1327-3042</t>
+          <t>0507-1432-9683</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경상남도 창원시 성산구 동산로65번길 24 타임빌딩 401호</t>
+          <t>경남 창원시 마산합포구 해안대로 91 3층 캡틴짐</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/fitness055sangnam</t>
+          <t>https://www.instagram.com/captaingym_wolyeong?igsh=a2x0NWNmcGNxdTAy</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,15 +797,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cq4z</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>598</v>
+        <v>830</v>
       </c>
       <c r="Q4" t="n">
-        <v>490</v>
+        <v>655</v>
       </c>
       <c r="R4" t="n">
-        <v>1088</v>
+        <v>1485</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +836,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2090289034</t>
+          <t>1454603225</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090289034</t>
+          <t>https://m.place.naver.com/place/1454603225</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>에어짐 용원본점 헬스&amp;PT</t>
+          <t>빅스짐 상남점 헬스 PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>changsgym@naver.com</t>
+          <t>bigsgymsangnam@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1411-7035</t>
+          <t>0507-1431-9683</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경상남도 창원시 진해구 용재로 18 뉴타운빌딩 7F</t>
+          <t>경남 창원시 성산구 마디미로43번길 10 모아엔트몰 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/air_gym640s?igsh=ZTBxdmJ3dHNsczg5&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/bigsgym_sangnam</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42kzm</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>301</v>
+        <v>1441</v>
       </c>
       <c r="Q5" t="n">
-        <v>434</v>
+        <v>755</v>
       </c>
       <c r="R5" t="n">
-        <v>735</v>
+        <v>2196</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,56 +934,56 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>320994196</t>
+          <t>1989922319</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/320994196</t>
+          <t>https://m.place.naver.com/place/1989922319</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>캡틴짐W 여성전용 헬스&amp;PT 창원팔용점</t>
+          <t>피트니스055 상남점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>captaingym_w@naver.com</t>
+          <t>fitness055_sangnam@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1354-9683</t>
+          <t>0507-1327-3042</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경상남도 창원시 의창구 팔용로 429 팔용프라자 5층 캡틴짐W</t>
+          <t>경남 창원시 성산구 동산로65번길 24 타임빌딩 401호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/captaingym_w</t>
+          <t>https://link.inpock.co.kr/fitness055sangnam</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w0x2m4b</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>425</v>
+        <v>618</v>
       </c>
       <c r="Q6" t="n">
-        <v>643</v>
+        <v>506</v>
       </c>
       <c r="R6" t="n">
-        <v>1068</v>
+        <v>1124</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1032,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1025206135</t>
+          <t>2090289034</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1025206135</t>
+          <t>https://m.place.naver.com/place/2090289034</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>휘트니스R 진해점 헬스&amp;PT&amp;필라테스</t>
+          <t>머슬그로우짐 중앙점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fitnessr@naver.com</t>
+          <t>rldhrrl1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1312-9066</t>
+          <t>0507-1425-9018</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경상남도 창원시 진해구 진해대로 742 석동H빌딩 5층 휘트니스R진해점</t>
+          <t>경남 창원시 성산구 중앙대로 89 2층 머슬그로우짐</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/fitnessr</t>
+          <t>https://www.instagram.com/musclegrowgym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1076,13 +1096,17 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcf6j8</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1655</v>
+        <v>831</v>
       </c>
       <c r="Q7" t="n">
-        <v>497</v>
+        <v>1341</v>
       </c>
       <c r="R7" t="n">
-        <v>2152</v>
+        <v>2172</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1130,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1353920850</t>
+          <t>36780621</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1353920850</t>
+          <t>https://m.place.naver.com/place/36780621</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>베러짐 헬스&amp;PT상남점</t>
+          <t>빅스짐 롯데백화점 창원점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bettergym0601@naver.com</t>
+          <t>bigsgymyh@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1415-6717</t>
+          <t>0507-1392-4523</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경상남도 창원시 성산구 마디미로 61 4층 베러짐</t>
+          <t>경남 창원시 성산구 상남로 121 8층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bettergym0601</t>
+          <t>https://www.instagram.com/bigsgym_lotte/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,15 +1189,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wa27pfo</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1173</v>
+        <v>161</v>
       </c>
       <c r="Q8" t="n">
-        <v>783</v>
+        <v>77</v>
       </c>
       <c r="R8" t="n">
-        <v>1956</v>
+        <v>238</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1623132310</t>
+          <t>2033209297</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1623132310</t>
+          <t>https://m.place.naver.com/place/2033209297</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;골프인 롯데마트 창원중앙점</t>
+          <t>캡틴짐 창원 상남점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>healthboygym87@naver.com</t>
+          <t>captaingym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1337-8691</t>
+          <t>0507-1352-9684</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경상남도 창원시 성산구 중앙대로 123 롯데마트맥스 창원중앙점 2층</t>
+          <t>경남 창원시 성산구 중앙대로 104 마이우스빌딩 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym87</t>
+          <t>https://blog.naver.com/captaingym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1264,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4642a</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>391</v>
+        <v>683</v>
       </c>
       <c r="Q9" t="n">
-        <v>380</v>
+        <v>250</v>
       </c>
       <c r="R9" t="n">
-        <v>771</v>
+        <v>933</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1697329635</t>
+          <t>1927544067</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1697329635</t>
+          <t>https://m.place.naver.com/place/1927544067</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>머슬팩토리 진해점 헬스&amp;PT&amp;필라테스&amp;요가</t>
+          <t>핏불휘트니스 마산점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>musclefactory_jinhae@naver.com</t>
+          <t>pb2911@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1357-9682</t>
+          <t>0507-1365-9682</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경상남도 창원시 진해구 충장로657번길 38 6층</t>
+          <t>경남 창원시 마산회원구 3·15대로 486 1층 핏불휘트니스</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/musclefactory_jinhae</t>
+          <t>https://blog.naver.com/pb2911</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1358,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4rl0g</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1017</v>
+        <v>1342</v>
       </c>
       <c r="Q10" t="n">
-        <v>626</v>
+        <v>705</v>
       </c>
       <c r="R10" t="n">
-        <v>1643</v>
+        <v>2047</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1625616756</t>
+          <t>1228287028</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1625616756</t>
+          <t>https://m.place.naver.com/place/1228287028</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1410,25 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>위트짐 봉곡점 헬스&amp;PT</t>
+          <t>센트럴피지오 PT&amp;필라테스 창원점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fitness055_bong@naver.com</t>
+          <t>central_physio@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1481-3514</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경상남도 창원시 의창구 원이대로 271 2층 위트짐</t>
+          <t>경남 창원시 성산구 용지로133번길 5 901호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitness055_bong</t>
+          <t>https://blog.naver.com/central_physio/223884089394?referrerCode=1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1448,13 +1488,17 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w7ji4vj</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1463,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>384</v>
+        <v>93</v>
       </c>
       <c r="Q11" t="n">
-        <v>612</v>
+        <v>220</v>
       </c>
       <c r="R11" t="n">
-        <v>996</v>
+        <v>313</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,957 +1522,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1145047054</t>
+          <t>2007613827</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1145047054</t>
+          <t>https://m.place.naver.com/place/2007613827</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>빅스짐 상남점 헬스 PT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>bigsgymsangnam@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1431-9683</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경상남도 창원시 성산구 마디미로43번길 10 모아엔트몰 4층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/bigsgym_sangnam</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>1436</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>753</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2189</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1989922319</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1989922319</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>피트니스055 팔용점 헬스&amp;PT</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>fitness055_paryong@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경상남도 창원시 의창구 팔용로 420 유토피아 상가 5층 501호</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/fitness055_paryong</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>485</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1155</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1640</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1481187801</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1481187801</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>바디퀸 헬스&amp;PT 마산월영점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>b_queen01@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1313-6693</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>경상남도 창원시 마산합포구 월영동서로 7 새마을회관 2층 바디퀸</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>http://pf.kakao.com/_BkSxhxj</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>150</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>67</v>
-      </c>
-      <c r="R14" t="n">
-        <v>217</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1639590011</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1639590011</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>피트니스마틴 봉곡점 헬스&amp;PT</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>martin7327@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1362-7327</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>경상남도 창원시 의창구 원이대로285번길 5 6층 602호</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ad08</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>430</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>430</v>
-      </c>
-      <c r="R15" t="n">
-        <v>860</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1515597172</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1515597172</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>캡틴짐 창원 상남점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>captaingym@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1352-9684</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>경상남도 창원시 성산구 중앙대로 104 마이우스빌딩 4층</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/captaingym</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>665</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>270</v>
-      </c>
-      <c r="R16" t="n">
-        <v>935</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1927544067</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1927544067</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>캡틴짐 마산 양덕점</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>captaingym@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1425-9682</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>경상남도 창원시 마산회원구 양덕북12길 113 경민인터빌상가 5층 캡틴짐 양덕점</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/captaingym</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>894</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>283</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1177</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1603752875</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1603752875</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>빅스짐 마산점</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>bigsmasan@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1314-3364</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>경상남도 창원시 마산회원구 용마로 130 메트로센텀 7층</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>http://www.instagram.com/bigsgym_masan</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>2347</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2007</v>
-      </c>
-      <c r="R18" t="n">
-        <v>4354</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1895942016</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1895942016</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>짐플릭스 창원상남점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>gymflix@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1426-2897</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>경상남도 창원시 성산구 마디미서로 34 8층</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://www.gymflix.co.kr</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>668</v>
-      </c>
-      <c r="R19" t="n">
-        <v>669</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>2026148875</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2026148875</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>하이바디짐 마산점</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>gmlrms116@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1477-5339</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>경상남도 창원시 마산합포구 해안대로 15 경민파라다이스 501호</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/gmlrms116</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>517</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>654</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1171</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1196073708</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1196073708</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>첼시피트니스&amp;PT 용원점</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>timegym055@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>055-552-5559</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>경상남도 창원시 진해구 용원로7번길 9 서정빌딩 5, 6층시그멀 피트니스&amp;PT</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/timegym055</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>138</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>172</v>
-      </c>
-      <c r="R21" t="n">
-        <v>310</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>37626856</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/37626856</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/창원_헬스장.xlsx
+++ b/naver-place-crawler/results_health/창원_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>빅스짐 중동점</t>
+          <t>메인핏 양덕2호점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bhy0565@naver.com</t>
+          <t>mainfit2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1349-8501</t>
+          <t>0507-1438-1778</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경남 창원시 의창구 중동중앙로 47 어반브릭스 오피스타워 21층</t>
+          <t>경남 창원시 마산회원구 봉양로 41 동원엠디스타 9,10층 3,4호 메인핏</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_jungdong/</t>
+          <t>https://map.naver.com/p/entry/place/1182203243?c=15.00,0,0,0,dh&amp;placePath=/ticket</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wce7fp</t>
+          <t>https://talk.naver.com/ct/w5xh92</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1318</v>
+        <v>388</v>
       </c>
       <c r="Q2" t="n">
-        <v>1580</v>
+        <v>554</v>
       </c>
       <c r="R2" t="n">
-        <v>2898</v>
+        <v>942</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,56 +640,56 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1259062125</t>
+          <t>1182203243</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1259062125</t>
+          <t>https://m.place.naver.com/place/1182203243</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>메인핏 양덕2호점</t>
+          <t>캡틴짐 헬스&amp;PT 24시 마산월영점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mainfit2@naver.com</t>
+          <t>captaingym_m@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1438-1778</t>
+          <t>0507-1432-9683</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경남 창원시 마산회원구 봉양로 41 동원엠디스타 9,10층 3,4호 메인핏</t>
+          <t>경남 창원시 마산합포구 해안대로 91 3층 캡틴짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://map.naver.com/p/entry/place/1182203243?c=15.00,0,0,0,dh&amp;placePath=/ticket</t>
+          <t>https://www.instagram.com/captaingym_wolyeong?igsh=a2x0NWNmcGNxdTAy</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5xh92</t>
+          <t>https://talk.naver.com/ct/w4cq4z</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>388</v>
+        <v>831</v>
       </c>
       <c r="Q3" t="n">
-        <v>554</v>
+        <v>655</v>
       </c>
       <c r="R3" t="n">
-        <v>942</v>
+        <v>1486</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,51 +738,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1182203243</t>
+          <t>1454603225</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1182203243</t>
+          <t>https://m.place.naver.com/place/1454603225</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>캡틴짐 헬스&amp;PT 24시 마산월영점</t>
+          <t>빅스짐 상남점 헬스 PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>captaingym_m@naver.com</t>
+          <t>bigsgymsangnam@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1432-9683</t>
+          <t>0507-1431-9683</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경남 창원시 마산합포구 해안대로 91 3층 캡틴짐</t>
+          <t>경남 창원시 성산구 마디미로43번길 10 모아엔트몰 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/captaingym_wolyeong?igsh=a2x0NWNmcGNxdTAy</t>
+          <t>https://www.instagram.com/bigsgym_sangnam</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4cq4z</t>
+          <t>https://talk.naver.com/ct/w42kzm</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>830</v>
+        <v>1443</v>
       </c>
       <c r="Q4" t="n">
-        <v>655</v>
+        <v>755</v>
       </c>
       <c r="R4" t="n">
-        <v>1485</v>
+        <v>2198</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,56 +836,56 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1454603225</t>
+          <t>1989922319</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1454603225</t>
+          <t>https://m.place.naver.com/place/1989922319</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>빅스짐 상남점 헬스 PT</t>
+          <t>피트니스055 상남점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bigsgymsangnam@naver.com</t>
+          <t>fitness055_sangnam@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1431-9683</t>
+          <t>0507-1327-3042</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 마디미로43번길 10 모아엔트몰 4층</t>
+          <t>경남 창원시 성산구 동산로65번길 24 타임빌딩 401호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_sangnam</t>
+          <t>https://link.inpock.co.kr/fitness055sangnam</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42kzm</t>
+          <t>https://talk.naver.com/ct/w0x2m4b</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1441</v>
+        <v>618</v>
       </c>
       <c r="Q5" t="n">
-        <v>755</v>
+        <v>506</v>
       </c>
       <c r="R5" t="n">
-        <v>2196</v>
+        <v>1124</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,56 +934,56 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1989922319</t>
+          <t>2090289034</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1989922319</t>
+          <t>https://m.place.naver.com/place/2090289034</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피트니스055 상남점 헬스&amp;PT</t>
+          <t>머슬팩토리 진해점 헬스&amp;PT&amp;필라테스&amp;요가</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fitness055_sangnam@naver.com</t>
+          <t>musclefactory_jinhae@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1327-3042</t>
+          <t>0507-1357-9682</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 동산로65번길 24 타임빌딩 401호</t>
+          <t>경남 창원시 진해구 충장로657번길 38 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/fitness055sangnam</t>
+          <t>https://blog.naver.com/musclefactory_jinhae</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w0x2m4b</t>
+          <t>https://talk.naver.com/ct/w4ru4g</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>618</v>
+        <v>1021</v>
       </c>
       <c r="Q6" t="n">
-        <v>506</v>
+        <v>631</v>
       </c>
       <c r="R6" t="n">
-        <v>1124</v>
+        <v>1652</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2090289034</t>
+          <t>1625616756</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090289034</t>
+          <t>https://m.place.naver.com/place/1625616756</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="Q7" t="n">
         <v>1341</v>
       </c>
       <c r="R7" t="n">
-        <v>2172</v>
+        <v>2175</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q8" t="n">
         <v>77</v>
       </c>
       <c r="R8" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1238,41 +1238,41 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>캡틴짐 창원 상남점</t>
+          <t>유즈핏 마산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>captaingym@naver.com</t>
+          <t>uzfitmasan@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1352-9684</t>
+          <t>0507-1444-3344</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 중앙대로 104 마이우스빌딩 4층</t>
+          <t>경남 창원시 마산회원구 합성남3길 21 3층 유즈핏</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/captaingym</t>
+          <t>https://youtube.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4642a</t>
+          <t>https://talk.naver.com/ct/wcsf02</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>683</v>
+        <v>324</v>
       </c>
       <c r="Q9" t="n">
-        <v>250</v>
+        <v>833</v>
       </c>
       <c r="R9" t="n">
-        <v>933</v>
+        <v>1157</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1927544067</t>
+          <t>1107292971</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1927544067</t>
+          <t>https://m.place.naver.com/place/1107292971</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1348,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>핏불휘트니스 마산점</t>
+          <t>캡틴짐 창원 상남점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pb2911@naver.com</t>
+          <t>captaingym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1365-9682</t>
+          <t>0507-1352-9684</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경남 창원시 마산회원구 3·15대로 486 1층 핏불휘트니스</t>
+          <t>경남 창원시 성산구 중앙대로 104 마이우스빌딩 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pb2911</t>
+          <t>https://blog.naver.com/captaingym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4rl0g</t>
+          <t>https://talk.naver.com/ct/w4642a</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1342</v>
+        <v>689</v>
       </c>
       <c r="Q10" t="n">
-        <v>705</v>
+        <v>250</v>
       </c>
       <c r="R10" t="n">
-        <v>2047</v>
+        <v>939</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1228287028</t>
+          <t>1927544067</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228287028</t>
+          <t>https://m.place.naver.com/place/1927544067</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1446,93 +1446,191 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>센트럴피지오 PT&amp;필라테스 창원점</t>
+          <t>유즈핏 창원점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>central_physio@naver.com</t>
+          <t>uzfit2@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1481-3514</t>
+          <t>0507-1365-6497</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>경남 창원시 의창구 용동로 85 1동 4층 405호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/uzfit_changwon</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4q40o</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>282</v>
+      </c>
+      <c r="R11" t="n">
+        <v>365</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1266126489</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1266126489</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>센트럴피지오 PT&amp;필라테스 창원점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>central_physio@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1481-3514</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>경남 창원시 성산구 용지로133번길 5 901호</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://blog.naver.com/central_physio/223884089394?referrerCode=1</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w7ji4vj</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>93</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>220</v>
-      </c>
-      <c r="R11" t="n">
-        <v>313</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>94</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>222</v>
+      </c>
+      <c r="R12" t="n">
+        <v>316</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>2007613827</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/2007613827</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/창원_헬스장.xlsx
+++ b/naver-place-crawler/results_health/창원_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -657,34 +657,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>캡틴짐 헬스&amp;PT 24시 마산월영점</t>
+          <t>위트짐 봉곡점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>captaingym_m@naver.com</t>
+          <t>fitness055_bong@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1432-9683</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경남 창원시 마산합포구 해안대로 91 3층 캡틴짐</t>
+          <t>경남 창원시 의창구 원이대로 271 2층 위트짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/captaingym_wolyeong?igsh=a2x0NWNmcGNxdTAy</t>
+          <t>https://blog.naver.com/fitness055_bong</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -699,19 +695,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4cq4z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>831</v>
+        <v>382</v>
       </c>
       <c r="Q3" t="n">
-        <v>655</v>
+        <v>622</v>
       </c>
       <c r="R3" t="n">
-        <v>1486</v>
+        <v>1004</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1454603225</t>
+          <t>1145047054</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1454603225</t>
+          <t>https://m.place.naver.com/place/1145047054</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,34 +747,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>빅스짐 상남점 헬스 PT</t>
+          <t>캡틴짐 헬스&amp;PT 24시 마산월영점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bigsgymsangnam@naver.com</t>
+          <t>captaingym_m@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1431-9683</t>
+          <t>0507-1432-9683</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 마디미로43번길 10 모아엔트몰 4층</t>
+          <t>경남 창원시 마산합포구 해안대로 91 3층 캡틴짐</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_sangnam</t>
+          <t>https://www.instagram.com/captaingym_wolyeong?igsh=a2x0NWNmcGNxdTAy</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +799,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42kzm</t>
+          <t>https://talk.naver.com/ct/w4cq4z</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1443</v>
+        <v>831</v>
       </c>
       <c r="Q4" t="n">
-        <v>755</v>
+        <v>655</v>
       </c>
       <c r="R4" t="n">
-        <v>2198</v>
+        <v>1486</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1989922319</t>
+          <t>1454603225</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1989922319</t>
+          <t>https://m.place.naver.com/place/1454603225</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -853,39 +845,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피트니스055 상남점 헬스&amp;PT</t>
+          <t>빅스짐 상남점 헬스 PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fitness055_sangnam@naver.com</t>
+          <t>bigsgymsangnam@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1327-3042</t>
+          <t>0507-1431-9683</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 동산로65번길 24 타임빌딩 401호</t>
+          <t>경남 창원시 성산구 마디미로43번길 10 모아엔트몰 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/fitness055sangnam</t>
+          <t>https://www.instagram.com/bigsgym_sangnam</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -895,7 +887,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +897,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w0x2m4b</t>
+          <t>https://talk.naver.com/ct/w42kzm</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>618</v>
+        <v>1443</v>
       </c>
       <c r="Q5" t="n">
-        <v>506</v>
+        <v>755</v>
       </c>
       <c r="R5" t="n">
-        <v>1124</v>
+        <v>2198</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2090289034</t>
+          <t>1989922319</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090289034</t>
+          <t>https://m.place.naver.com/place/1989922319</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -951,39 +943,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>머슬팩토리 진해점 헬스&amp;PT&amp;필라테스&amp;요가</t>
+          <t>피트니스055 상남점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>musclefactory_jinhae@naver.com</t>
+          <t>fitness055_sangnam@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1357-9682</t>
+          <t>0507-1327-3042</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경남 창원시 진해구 충장로657번길 38 6층</t>
+          <t>경남 창원시 성산구 동산로65번길 24 타임빌딩 401호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/musclefactory_jinhae</t>
+          <t>https://link.inpock.co.kr/fitness055sangnam</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1003,7 +995,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ru4g</t>
+          <t>https://talk.naver.com/ct/w0x2m4b</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1021</v>
+        <v>618</v>
       </c>
       <c r="Q6" t="n">
-        <v>631</v>
+        <v>506</v>
       </c>
       <c r="R6" t="n">
-        <v>1652</v>
+        <v>1124</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1625616756</t>
+          <t>2090289034</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1625616756</t>
+          <t>https://m.place.naver.com/place/2090289034</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>머슬그로우짐 중앙점</t>
+          <t>머슬팩토리 진해점 헬스&amp;PT&amp;필라테스&amp;요가</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rldhrrl1@naver.com</t>
+          <t>musclefactory_jinhae@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1425-9018</t>
+          <t>0507-1357-9682</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 중앙대로 89 2층 머슬그로우짐</t>
+          <t>경남 창원시 진해구 충장로657번길 38 6층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/musclegrowgym</t>
+          <t>https://blog.naver.com/musclefactory_jinhae</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1083,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcf6j8</t>
+          <t>https://talk.naver.com/ct/w4ru4g</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>834</v>
+        <v>1021</v>
       </c>
       <c r="Q7" t="n">
-        <v>1341</v>
+        <v>631</v>
       </c>
       <c r="R7" t="n">
-        <v>2175</v>
+        <v>1652</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>36780621</t>
+          <t>1625616756</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36780621</t>
+          <t>https://m.place.naver.com/place/1625616756</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,29 +1144,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>빅스짐 롯데백화점 창원점</t>
+          <t>머슬그로우짐 중앙점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bigsgymyh@naver.com</t>
+          <t>rldhrrl1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1392-4523</t>
+          <t>0507-1425-9018</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 상남로 121 8층</t>
+          <t>경남 창원시 성산구 중앙대로 89 2층 머슬그로우짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_lotte/</t>
+          <t>https://www.instagram.com/musclegrowgym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wa27pfo</t>
+          <t>https://talk.naver.com/ct/wcf6j8</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>162</v>
+        <v>834</v>
       </c>
       <c r="Q8" t="n">
-        <v>77</v>
+        <v>1341</v>
       </c>
       <c r="R8" t="n">
-        <v>239</v>
+        <v>2175</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2033209297</t>
+          <t>36780621</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033209297</t>
+          <t>https://m.place.naver.com/place/36780621</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>유즈핏 마산점</t>
+          <t>빅스짐 롯데백화점 창원점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>uzfitmasan@naver.com</t>
+          <t>bigsgymyh@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1444-3344</t>
+          <t>0507-1392-4523</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경남 창원시 마산회원구 합성남3길 21 3층 유즈핏</t>
+          <t>경남 창원시 성산구 상남로 121 8층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://youtube.com/</t>
+          <t>https://www.instagram.com/bigsgym_lotte/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcsf02</t>
+          <t>https://talk.naver.com/ct/wa27pfo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>324</v>
+        <v>162</v>
       </c>
       <c r="Q9" t="n">
-        <v>833</v>
+        <v>77</v>
       </c>
       <c r="R9" t="n">
-        <v>1157</v>
+        <v>239</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1107292971</t>
+          <t>2033209297</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1107292971</t>
+          <t>https://m.place.naver.com/place/2033209297</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1412,10 +1404,10 @@
         <v>689</v>
       </c>
       <c r="Q10" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="R10" t="n">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1446,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>유즈핏 창원점</t>
+          <t>센트럴피지오 PT&amp;필라테스 창원점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uzfit2@naver.com</t>
+          <t>central_physio@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1365-6497</t>
+          <t>0507-1481-3514</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경남 창원시 의창구 용동로 85 1동 4층 405호</t>
+          <t>경남 창원시 성산구 용지로133번길 5 901호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uzfit_changwon</t>
+          <t>https://blog.naver.com/central_physio/223884089394?referrerCode=1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1483,7 +1475,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,12 +1485,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4q40o</t>
+          <t>https://talk.naver.com/ct/w7ji4vj</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1507,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Q11" t="n">
-        <v>282</v>
+        <v>222</v>
       </c>
       <c r="R11" t="n">
-        <v>365</v>
+        <v>316</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,113 +1514,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1266126489</t>
+          <t>2007613827</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1266126489</t>
+          <t>https://m.place.naver.com/place/2007613827</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>센트럴피지오 PT&amp;필라테스 창원점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>central_physio@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1481-3514</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경남 창원시 성산구 용지로133번길 5 901호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/central_physio/223884089394?referrerCode=1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7ji4vj</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>222</v>
-      </c>
-      <c r="R12" t="n">
-        <v>316</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2007613827</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2007613827</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/창원_헬스장.xlsx
+++ b/naver-place-crawler/results_health/창원_헬스장.xlsx
@@ -417,12 +417,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -591,7 +591,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -718,10 +718,10 @@
         <v>382</v>
       </c>
       <c r="Q3" t="n">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="R3" t="n">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="Q5" t="n">
         <v>755</v>
       </c>
       <c r="R5" t="n">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1046,29 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>머슬팩토리 진해점 헬스&amp;PT&amp;필라테스&amp;요가</t>
+          <t>헬스보이짐&amp;골프인 롯데마트 창원중앙점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>musclefactory_jinhae@naver.com</t>
+          <t>healthboygym87@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1357-9682</t>
+          <t>0507-1337-8691</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경남 창원시 진해구 충장로657번길 38 6층</t>
+          <t>경남 창원시 성산구 중앙대로 123 롯데마트맥스 창원중앙점 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/musclefactory_jinhae</t>
+          <t>https://blog.naver.com/healthboygym87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ru4g</t>
+          <t>https://talk.naver.com/ct/womn74a</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1021</v>
+        <v>395</v>
       </c>
       <c r="Q7" t="n">
-        <v>631</v>
+        <v>392</v>
       </c>
       <c r="R7" t="n">
-        <v>1652</v>
+        <v>787</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1625616756</t>
+          <t>1697329635</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1625616756</t>
+          <t>https://m.place.naver.com/place/1697329635</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1335,34 +1335,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>캡틴짐 창원 상남점</t>
+          <t>준피트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>captaingym@naver.com</t>
+          <t>junfit26@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1352-9684</t>
+          <t>0507-1349-6855</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 중앙대로 104 마이우스빌딩 4층</t>
+          <t>경남 창원시 마산회원구 율림교로 13 4층 401호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/captaingym</t>
+          <t>https://www.instagram.com/junfitness2026/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4642a</t>
+          <t>https://talk.naver.com/ct/wk9621e</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>689</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>251</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>940</v>
+        <v>25</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1927544067</t>
+          <t>2022834325</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1927544067</t>
+          <t>https://m.place.naver.com/place/2022834325</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1433,34 +1433,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>센트럴피지오 PT&amp;필라테스 창원점</t>
+          <t>모브짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>central_physio@naver.com</t>
+          <t>movgym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1481-3514</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 용지로133번길 5 901호</t>
+          <t>경남 창원시 성산구 창원천로 288 대동그린코아상가 5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/central_physio/223884089394?referrerCode=1</t>
+          <t>https://blog.naver.com/movgym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1480,17 +1476,13 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7ji4vj</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1499,13 +1491,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>94</v>
+        <v>231</v>
       </c>
       <c r="Q11" t="n">
-        <v>222</v>
+        <v>361</v>
       </c>
       <c r="R11" t="n">
-        <v>316</v>
+        <v>592</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,15 +1506,211 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2007613827</t>
+          <t>1390138586</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007613827</t>
+          <t>https://m.place.naver.com/place/1390138586</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>브레이브짐</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bravegym@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1342-9682</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경남 창원시 마산회원구 북성로 125 202,203호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bravegym</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42vi2</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>204</v>
+      </c>
+      <c r="R12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1856639930</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1856639930</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>캡틴짐 창원 상남점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>captaingym@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1352-9684</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경남 창원시 성산구 중앙대로 104 마이우스빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/captaingym</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4642a</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>689</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>251</v>
+      </c>
+      <c r="R13" t="n">
+        <v>940</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1927544067</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1927544067</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/창원_헬스장.xlsx
+++ b/naver-place-crawler/results_health/창원_헬스장.xlsx
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="Q4" t="n">
         <v>655</v>
       </c>
       <c r="R4" t="n">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="Q5" t="n">
         <v>755</v>
       </c>
       <c r="R5" t="n">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>834</v>
+        <v>839</v>
       </c>
       <c r="Q8" t="n">
         <v>1341</v>
       </c>
       <c r="R8" t="n">
-        <v>2175</v>
+        <v>2180</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1303,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q9" t="n">
         <v>77</v>
       </c>
       <c r="R9" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1592,10 +1592,10 @@
         <v>46</v>
       </c>
       <c r="Q12" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="R12" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/창원_헬스장.xlsx
+++ b/naver-place-crawler/results_health/창원_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://map.naver.com/p/entry/place/1182203243?c=15.00,0,0,0,dh&amp;placePath=/ticket</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -650,37 +650,41 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>위트짐 봉곡점 헬스&amp;PT</t>
+          <t>캡틴짐 헬스&amp;PT 24시 마산월영점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fitness055_bong@naver.com</t>
+          <t>captaingym_m@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1432-9683</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경남 창원시 의창구 원이대로 271 2층 위트짐</t>
+          <t>경남 창원시 마산합포구 해안대로 91 3층 캡틴짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitness055_bong</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,20 +694,24 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4cq4z</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>382</v>
+        <v>832</v>
       </c>
       <c r="Q3" t="n">
-        <v>624</v>
+        <v>655</v>
       </c>
       <c r="R3" t="n">
-        <v>1006</v>
+        <v>1487</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +738,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1145047054</t>
+          <t>1454603225</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1145047054</t>
+          <t>https://m.place.naver.com/place/1454603225</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>캡틴짐 헬스&amp;PT 24시 마산월영점</t>
+          <t>빅스짐 상남점 헬스 PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>captaingym_m@naver.com</t>
+          <t>bigsgymsangnam@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1432-9683</t>
+          <t>0507-1431-9683</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경남 창원시 마산합포구 해안대로 91 3층 캡틴짐</t>
+          <t>경남 창원시 성산구 마디미로43번길 10 모아엔트몰 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/captaingym_wolyeong?igsh=a2x0NWNmcGNxdTAy</t>
+          <t>https://www.instagram.com/bigsgym_sangnam</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -799,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4cq4z</t>
+          <t>https://talk.naver.com/ct/w42kzm</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>832</v>
+        <v>1443</v>
       </c>
       <c r="Q4" t="n">
-        <v>655</v>
+        <v>755</v>
       </c>
       <c r="R4" t="n">
-        <v>1487</v>
+        <v>2198</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,56 +836,56 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1454603225</t>
+          <t>1989922319</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1454603225</t>
+          <t>https://m.place.naver.com/place/1989922319</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>빅스짐 상남점 헬스 PT</t>
+          <t>피트니스055 상남점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bigsgymsangnam@naver.com</t>
+          <t>fitness055_sangnam@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1431-9683</t>
+          <t>0507-1327-3042</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 마디미로43번길 10 모아엔트몰 4층</t>
+          <t>경남 창원시 성산구 동산로65번길 24 타임빌딩 401호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_sangnam</t>
+          <t>https://link.inpock.co.kr/fitness055sangnam</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -887,7 +895,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -897,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42kzm</t>
+          <t>https://talk.naver.com/ct/w0x2m4b</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -911,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1443</v>
+        <v>618</v>
       </c>
       <c r="Q5" t="n">
-        <v>755</v>
+        <v>506</v>
       </c>
       <c r="R5" t="n">
-        <v>2198</v>
+        <v>1124</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -926,56 +934,56 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1989922319</t>
+          <t>2090289034</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1989922319</t>
+          <t>https://m.place.naver.com/place/2090289034</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피트니스055 상남점 헬스&amp;PT</t>
+          <t>헬스보이짐&amp;골프인 롯데마트 창원중앙점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fitness055_sangnam@naver.com</t>
+          <t>healthboygym87@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1327-3042</t>
+          <t>0507-1337-8691</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 동산로65번길 24 타임빌딩 401호</t>
+          <t>경남 창원시 성산구 중앙대로 123 롯데마트맥스 창원중앙점 2층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/fitness055sangnam</t>
+          <t>https://blog.naver.com/healthboygym87</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -995,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w0x2m4b</t>
+          <t>https://talk.naver.com/ct/womn74a</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1009,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>618</v>
+        <v>395</v>
       </c>
       <c r="Q6" t="n">
-        <v>506</v>
+        <v>392</v>
       </c>
       <c r="R6" t="n">
-        <v>1124</v>
+        <v>787</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1024,17 +1032,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2090289034</t>
+          <t>1697329635</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090289034</t>
+          <t>https://m.place.naver.com/place/1697329635</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1046,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;골프인 롯데마트 창원중앙점</t>
+          <t>머슬그로우짐 중앙점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>healthboygym87@naver.com</t>
+          <t>rldhrrl1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1337-8691</t>
+          <t>0507-1425-9018</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 중앙대로 123 롯데마트맥스 창원중앙점 2층</t>
+          <t>경남 창원시 성산구 중앙대로 89 2층 머슬그로우짐</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym87</t>
+          <t>https://www.instagram.com/musclegrowgym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1093,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/womn74a</t>
+          <t>https://talk.naver.com/ct/wcf6j8</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>395</v>
+        <v>840</v>
       </c>
       <c r="Q7" t="n">
-        <v>392</v>
+        <v>1341</v>
       </c>
       <c r="R7" t="n">
-        <v>787</v>
+        <v>2181</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1697329635</t>
+          <t>36780621</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1697329635</t>
+          <t>https://m.place.naver.com/place/36780621</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1144,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>머슬그로우짐 중앙점</t>
+          <t>빅스짐 롯데백화점 창원점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rldhrrl1@naver.com</t>
+          <t>bigsgymyh@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1425-9018</t>
+          <t>0507-1392-4523</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 중앙대로 89 2층 머슬그로우짐</t>
+          <t>경남 창원시 성산구 상남로 121 8층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/musclegrowgym</t>
+          <t>https://www.instagram.com/bigsgym_lotte/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1191,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcf6j8</t>
+          <t>https://talk.naver.com/ct/wa27pfo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>839</v>
+        <v>163</v>
       </c>
       <c r="Q8" t="n">
-        <v>1341</v>
+        <v>77</v>
       </c>
       <c r="R8" t="n">
-        <v>2180</v>
+        <v>240</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,17 +1228,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36780621</t>
+          <t>2033209297</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36780621</t>
+          <t>https://m.place.naver.com/place/2033209297</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1242,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>빅스짐 롯데백화점 창원점</t>
+          <t>유즈핏 마산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bigsgymyh@naver.com</t>
+          <t>uzfitmasan@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1392-4523</t>
+          <t>0507-1444-3344</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 상남로 121 8층</t>
+          <t>경남 창원시 마산회원구 합성남3길 21 3층 유즈핏</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_lotte/</t>
+          <t>https://youtube.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1289,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wa27pfo</t>
+          <t>https://talk.naver.com/ct/wcsf02</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>163</v>
+        <v>324</v>
       </c>
       <c r="Q9" t="n">
-        <v>77</v>
+        <v>833</v>
       </c>
       <c r="R9" t="n">
-        <v>240</v>
+        <v>1157</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,51 +1326,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2033209297</t>
+          <t>1107292971</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033209297</t>
+          <t>https://m.place.naver.com/place/1107292971</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>준피트니스</t>
+          <t>캡틴짐 창원 상남점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>junfit26@naver.com</t>
+          <t>captaingym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1349-6855</t>
+          <t>0507-1352-9684</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경남 창원시 마산회원구 율림교로 13 4층 401호</t>
+          <t>경남 창원시 성산구 중앙대로 104 마이우스빌딩 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/junfitness2026/</t>
+          <t>https://blog.naver.com/captaingym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1377,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1387,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wk9621e</t>
+          <t>https://talk.naver.com/ct/w4642a</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>689</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="R10" t="n">
-        <v>25</v>
+        <v>940</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,47 +1424,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2022834325</t>
+          <t>1927544067</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2022834325</t>
+          <t>https://m.place.naver.com/place/1927544067</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>모브짐</t>
+          <t>유즈핏 창원점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>movgym@naver.com</t>
+          <t>uzfit2@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1365-6497</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 창원천로 288 대동그린코아상가 5층</t>
+          <t>경남 창원시 의창구 용동로 85 1동 4층 405호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/movgym</t>
+          <t>https://www.instagram.com/uzfit_changwon</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1471,15 +1483,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4q40o</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1491,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>231</v>
+        <v>83</v>
       </c>
       <c r="Q11" t="n">
-        <v>361</v>
+        <v>282</v>
       </c>
       <c r="R11" t="n">
-        <v>592</v>
+        <v>365</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1506,51 +1522,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1390138586</t>
+          <t>1266126489</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1390138586</t>
+          <t>https://m.place.naver.com/place/1266126489</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>브레이브짐</t>
+          <t>센트럴피지오 PT&amp;필라테스 창원점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>bravegym@naver.com</t>
+          <t>central_physio@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1342-9682</t>
+          <t>0507-1481-3514</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경남 창원시 마산회원구 북성로 125 202,203호</t>
+          <t>경남 창원시 성산구 용지로133번길 5 901호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bravegym</t>
+          <t>https://blog.naver.com/central_physio/223884089394?referrerCode=1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1575,12 +1591,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42vi2</t>
+          <t>https://talk.naver.com/ct/w7ji4vj</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1589,13 +1605,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="Q12" t="n">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="R12" t="n">
-        <v>252</v>
+        <v>317</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1604,115 +1620,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1856639930</t>
+          <t>2007613827</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1856639930</t>
+          <t>https://m.place.naver.com/place/2007613827</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>캡틴짐 창원 상남점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>captaingym@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1352-9684</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경남 창원시 성산구 중앙대로 104 마이우스빌딩 4층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/captaingym</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4642a</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>689</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>251</v>
-      </c>
-      <c r="R13" t="n">
-        <v>940</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1927544067</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1927544067</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/창원_헬스장.xlsx
+++ b/naver-place-crawler/results_health/창원_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -586,17 +586,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://map.naver.com/p/entry/place/1182203243?c=15.00,0,0,0,dh&amp;placePath=/ticket</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -657,34 +657,30 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>캡틴짐 헬스&amp;PT 24시 마산월영점</t>
+          <t>위트짐 봉곡점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>captaingym_m@naver.com</t>
+          <t>fitness055_bong@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1432-9683</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경남 창원시 마산합포구 해안대로 91 3층 캡틴짐</t>
+          <t>경남 창원시 의창구 원이대로 271 2층 위트짐</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fitness055_bong</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,24 +690,20 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4cq4z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>832</v>
+        <v>382</v>
       </c>
       <c r="Q3" t="n">
-        <v>655</v>
+        <v>624</v>
       </c>
       <c r="R3" t="n">
-        <v>1487</v>
+        <v>1006</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1454603225</t>
+          <t>1145047054</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1454603225</t>
+          <t>https://m.place.naver.com/place/1145047054</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -755,34 +747,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>빅스짐 상남점 헬스 PT</t>
+          <t>캡틴짐 헬스&amp;PT 24시 마산월영점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bigsgymsangnam@naver.com</t>
+          <t>captaingym_m@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1431-9683</t>
+          <t>0507-1432-9683</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 마디미로43번길 10 모아엔트몰 4층</t>
+          <t>경남 창원시 마산합포구 해안대로 91 3층 캡틴짐</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_sangnam</t>
+          <t>https://www.instagram.com/captaingym_wolyeong?igsh=a2x0NWNmcGNxdTAy</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +799,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42kzm</t>
+          <t>https://talk.naver.com/ct/w4cq4z</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +813,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1443</v>
+        <v>832</v>
       </c>
       <c r="Q4" t="n">
-        <v>755</v>
+        <v>655</v>
       </c>
       <c r="R4" t="n">
-        <v>2198</v>
+        <v>1487</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +828,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1989922319</t>
+          <t>1454603225</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1989922319</t>
+          <t>https://m.place.naver.com/place/1454603225</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -853,39 +845,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피트니스055 상남점 헬스&amp;PT</t>
+          <t>빅스짐 상남점 헬스 PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fitness055_sangnam@naver.com</t>
+          <t>bigsgymsangnam@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1327-3042</t>
+          <t>0507-1431-9683</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 동산로65번길 24 타임빌딩 401호</t>
+          <t>경남 창원시 성산구 마디미로43번길 10 모아엔트몰 4층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://link.inpock.co.kr/fitness055sangnam</t>
+          <t>https://www.instagram.com/bigsgym_sangnam</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -895,7 +887,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -905,7 +897,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w0x2m4b</t>
+          <t>https://talk.naver.com/ct/w42kzm</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +911,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>618</v>
+        <v>1443</v>
       </c>
       <c r="Q5" t="n">
-        <v>506</v>
+        <v>757</v>
       </c>
       <c r="R5" t="n">
-        <v>1124</v>
+        <v>2200</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +926,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2090289034</t>
+          <t>1989922319</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2090289034</t>
+          <t>https://m.place.naver.com/place/1989922319</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -951,39 +943,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;골프인 롯데마트 창원중앙점</t>
+          <t>피트니스055 상남점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboygym87@naver.com</t>
+          <t>fitness055_sangnam@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1337-8691</t>
+          <t>0507-1327-3042</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 중앙대로 123 롯데마트맥스 창원중앙점 2층</t>
+          <t>경남 창원시 성산구 동산로65번길 24 타임빌딩 401호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym87</t>
+          <t>https://link.inpock.co.kr/fitness055sangnam</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1003,7 +995,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/womn74a</t>
+          <t>https://talk.naver.com/ct/w0x2m4b</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1009,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>395</v>
+        <v>618</v>
       </c>
       <c r="Q6" t="n">
-        <v>392</v>
+        <v>506</v>
       </c>
       <c r="R6" t="n">
-        <v>787</v>
+        <v>1124</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1024,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1697329635</t>
+          <t>2090289034</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1697329635</t>
+          <t>https://m.place.naver.com/place/2090289034</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1046,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>머슬그로우짐 중앙점</t>
+          <t>헬스보이짐&amp;골프인 롯데마트 창원중앙점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rldhrrl1@naver.com</t>
+          <t>healthboygym87@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1425-9018</t>
+          <t>0507-1337-8691</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 중앙대로 89 2층 머슬그로우짐</t>
+          <t>경남 창원시 성산구 중앙대로 123 롯데마트맥스 창원중앙점 2층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/musclegrowgym</t>
+          <t>https://blog.naver.com/healthboygym87</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1083,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1093,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcf6j8</t>
+          <t>https://talk.naver.com/ct/womn74a</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1107,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>840</v>
+        <v>395</v>
       </c>
       <c r="Q7" t="n">
-        <v>1341</v>
+        <v>392</v>
       </c>
       <c r="R7" t="n">
-        <v>2181</v>
+        <v>787</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1122,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>36780621</t>
+          <t>1697329635</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36780621</t>
+          <t>https://m.place.naver.com/place/1697329635</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,29 +1144,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>빅스짐 롯데백화점 창원점</t>
+          <t>머슬그로우짐 중앙점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bigsgymyh@naver.com</t>
+          <t>rldhrrl1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1392-4523</t>
+          <t>0507-1425-9018</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 상남로 121 8층</t>
+          <t>경남 창원시 성산구 중앙대로 89 2층 머슬그로우짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_lotte/</t>
+          <t>https://www.instagram.com/musclegrowgym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1191,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wa27pfo</t>
+          <t>https://talk.naver.com/ct/wcf6j8</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>163</v>
+        <v>841</v>
       </c>
       <c r="Q8" t="n">
-        <v>77</v>
+        <v>1341</v>
       </c>
       <c r="R8" t="n">
-        <v>240</v>
+        <v>2182</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1220,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2033209297</t>
+          <t>36780621</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033209297</t>
+          <t>https://m.place.naver.com/place/36780621</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1242,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>유즈핏 마산점</t>
+          <t>빅스짐 롯데백화점 창원점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>uzfitmasan@naver.com</t>
+          <t>bigsgymyh@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1444-3344</t>
+          <t>0507-1392-4523</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경남 창원시 마산회원구 합성남3길 21 3층 유즈핏</t>
+          <t>경남 창원시 성산구 상남로 121 8층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://youtube.com/</t>
+          <t>https://www.instagram.com/bigsgym_lotte/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcsf02</t>
+          <t>https://talk.naver.com/ct/wa27pfo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>324</v>
+        <v>163</v>
       </c>
       <c r="Q9" t="n">
-        <v>833</v>
+        <v>82</v>
       </c>
       <c r="R9" t="n">
-        <v>1157</v>
+        <v>245</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1318,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1107292971</t>
+          <t>2033209297</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1107292971</t>
+          <t>https://m.place.naver.com/place/2033209297</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1446,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>유즈핏 창원점</t>
+          <t>센트럴피지오 PT&amp;필라테스 창원점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uzfit2@naver.com</t>
+          <t>central_physio@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1365-6497</t>
+          <t>0507-1481-3514</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경남 창원시 의창구 용동로 85 1동 4층 405호</t>
+          <t>경남 창원시 성산구 용지로133번길 5 901호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/uzfit_changwon</t>
+          <t>https://blog.naver.com/central_physio/223884089394?referrerCode=1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1483,7 +1475,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,12 +1485,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4q40o</t>
+          <t>https://talk.naver.com/ct/w7ji4vj</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1507,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Q11" t="n">
-        <v>282</v>
+        <v>223</v>
       </c>
       <c r="R11" t="n">
-        <v>365</v>
+        <v>317</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,113 +1514,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1266126489</t>
+          <t>2007613827</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1266126489</t>
+          <t>https://m.place.naver.com/place/2007613827</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>센트럴피지오 PT&amp;필라테스 창원점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>central_physio@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1481-3514</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경남 창원시 성산구 용지로133번길 5 901호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/central_physio/223884089394?referrerCode=1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w7ji4vj</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>94</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>223</v>
-      </c>
-      <c r="R12" t="n">
-        <v>317</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2007613827</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2007613827</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/창원_헬스장.xlsx
+++ b/naver-place-crawler/results_health/창원_헬스장.xlsx
@@ -417,11 +417,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -564,34 +564,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>메인핏 양덕2호점</t>
+          <t>빅스짐 중동점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mainfit2@naver.com</t>
+          <t>bhy0565@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1438-1778</t>
+          <t>0507-1349-8501</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경남 창원시 마산회원구 봉양로 41 동원엠디스타 9,10층 3,4호 메인핏</t>
+          <t>경남 창원시 의창구 중동중앙로 47 어반브릭스 오피스타워 21층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://map.naver.com/p/entry/place/1182203243?c=15.00,0,0,0,dh&amp;placePath=/ticket</t>
+          <t>https://www.instagram.com/bigsgym_jungdong/</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5xh92</t>
+          <t>https://talk.naver.com/ct/wce7fp</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>388</v>
+        <v>1318</v>
       </c>
       <c r="Q2" t="n">
-        <v>554</v>
+        <v>1583</v>
       </c>
       <c r="R2" t="n">
-        <v>942</v>
+        <v>2901</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1182203243</t>
+          <t>1259062125</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1182203243</t>
+          <t>https://m.place.naver.com/place/1259062125</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -662,30 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>위트짐 봉곡점 헬스&amp;PT</t>
+          <t>메인핏 양덕2호점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fitness055_bong@naver.com</t>
+          <t>mainfit2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0507-1438-1778</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경남 창원시 의창구 원이대로 271 2층 위트짐</t>
+          <t>경남 창원시 마산회원구 봉양로 41 동원엠디스타 9,10층 3,4호 메인핏</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitness055_bong</t>
+          <t>https://map.naver.com/p/entry/place/1182203243?c=15.00,0,0,0,dh&amp;placePath=/ticket</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -695,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5xh92</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="Q3" t="n">
-        <v>624</v>
+        <v>554</v>
       </c>
       <c r="R3" t="n">
-        <v>1006</v>
+        <v>942</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1145047054</t>
+          <t>1182203243</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1145047054</t>
+          <t>https://m.place.naver.com/place/1182203243</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -813,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="Q4" t="n">
         <v>655</v>
       </c>
       <c r="R4" t="n">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -911,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="Q5" t="n">
         <v>757</v>
       </c>
       <c r="R5" t="n">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1046,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>헬스보이짐&amp;골프인 롯데마트 창원중앙점</t>
+          <t>머슬그로우짐 중앙점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>healthboygym87@naver.com</t>
+          <t>rldhrrl1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1337-8691</t>
+          <t>0507-1425-9018</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 중앙대로 123 롯데마트맥스 창원중앙점 2층</t>
+          <t>경남 창원시 성산구 중앙대로 89 2층 머슬그로우짐</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym87</t>
+          <t>https://www.instagram.com/musclegrowgym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1083,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1093,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/womn74a</t>
+          <t>https://talk.naver.com/ct/wcf6j8</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1107,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>395</v>
+        <v>841</v>
       </c>
       <c r="Q7" t="n">
-        <v>392</v>
+        <v>1341</v>
       </c>
       <c r="R7" t="n">
-        <v>787</v>
+        <v>2182</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1122,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1697329635</t>
+          <t>36780621</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1697329635</t>
+          <t>https://m.place.naver.com/place/36780621</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1144,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>머슬그로우짐 중앙점</t>
+          <t>빅스짐 롯데백화점 창원점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rldhrrl1@naver.com</t>
+          <t>bigsgymyh@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1425-9018</t>
+          <t>0507-1392-4523</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 중앙대로 89 2층 머슬그로우짐</t>
+          <t>경남 창원시 성산구 상남로 121 8층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/musclegrowgym</t>
+          <t>https://www.instagram.com/bigsgym_lotte/</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1191,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcf6j8</t>
+          <t>https://talk.naver.com/ct/wa27pfo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1205,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>841</v>
+        <v>164</v>
       </c>
       <c r="Q8" t="n">
-        <v>1341</v>
+        <v>82</v>
       </c>
       <c r="R8" t="n">
-        <v>2182</v>
+        <v>246</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1220,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>36780621</t>
+          <t>2033209297</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36780621</t>
+          <t>https://m.place.naver.com/place/2033209297</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1242,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>빅스짐 롯데백화점 창원점</t>
+          <t>준피트니스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bigsgymyh@naver.com</t>
+          <t>junfit26@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1392-4523</t>
+          <t>0507-1349-6855</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 상남로 121 8층</t>
+          <t>경남 창원시 마산회원구 율림교로 13 4층 401호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_lotte/</t>
+          <t>https://www.instagram.com/junfitness2026/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1289,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wa27pfo</t>
+          <t>https://talk.naver.com/ct/wk9621e</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1303,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>163</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>82</v>
+        <v>15</v>
       </c>
       <c r="R9" t="n">
-        <v>245</v>
+        <v>25</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2033209297</t>
+          <t>2022834325</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033209297</t>
+          <t>https://m.place.naver.com/place/2022834325</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1335,34 +1343,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>캡틴짐 창원 상남점</t>
+          <t>모브짐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>captaingym@naver.com</t>
+          <t>movgym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1352-9684</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 중앙대로 104 마이우스빌딩 4층</t>
+          <t>경남 창원시 성산구 창원천로 288 대동그린코아상가 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/captaingym</t>
+          <t>https://blog.naver.com/movgym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1382,14 +1386,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4642a</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>689</v>
+        <v>231</v>
       </c>
       <c r="Q10" t="n">
-        <v>251</v>
+        <v>361</v>
       </c>
       <c r="R10" t="n">
-        <v>940</v>
+        <v>592</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1927544067</t>
+          <t>1390138586</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1927544067</t>
+          <t>https://m.place.naver.com/place/1390138586</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1438,29 +1438,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>센트럴피지오 PT&amp;필라테스 창원점</t>
+          <t>캡틴짐 창원 상남점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>central_physio@naver.com</t>
+          <t>captaingym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1481-3514</t>
+          <t>0507-1352-9684</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 용지로133번길 5 901호</t>
+          <t>경남 창원시 성산구 중앙대로 104 마이우스빌딩 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/central_physio/223884089394?referrerCode=1</t>
+          <t>https://blog.naver.com/captaingym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w7ji4vj</t>
+          <t>https://talk.naver.com/ct/w4642a</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>94</v>
+        <v>691</v>
       </c>
       <c r="Q11" t="n">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="R11" t="n">
-        <v>317</v>
+        <v>942</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,15 +1514,113 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2007613827</t>
+          <t>1927544067</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2007613827</t>
+          <t>https://m.place.naver.com/place/1927544067</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>핏불휘트니스 마산점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>pb2911@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1365-9682</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>경남 창원시 마산회원구 3·15대로 486 1층 핏불휘트니스</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pb2911</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4rl0g</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1350</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>705</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2055</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1228287028</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1228287028</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>

--- a/naver-place-crawler/results_health/창원_헬스장.xlsx
+++ b/naver-place-crawler/results_health/창원_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="Q6" t="n">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="R6" t="n">
-        <v>1124</v>
+        <v>1134</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q8" t="n">
         <v>82</v>
       </c>
       <c r="R8" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1336,37 +1336,41 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>모브짐</t>
+          <t>캡틴짐 창원 상남점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>movgym@naver.com</t>
+          <t>captaingym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1352-9684</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 창원천로 288 대동그린코아상가 5층</t>
+          <t>경남 창원시 성산구 중앙대로 104 마이우스빌딩 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/movgym</t>
+          <t>https://blog.naver.com/captaingym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1386,10 +1390,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4642a</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1401,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>231</v>
+        <v>692</v>
       </c>
       <c r="Q10" t="n">
-        <v>361</v>
+        <v>251</v>
       </c>
       <c r="R10" t="n">
-        <v>592</v>
+        <v>943</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1416,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1390138586</t>
+          <t>1927544067</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1390138586</t>
+          <t>https://m.place.naver.com/place/1927544067</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1438,29 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>캡틴짐 창원 상남점</t>
+          <t>핏불휘트니스 마산점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>captaingym@naver.com</t>
+          <t>pb2911@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1352-9684</t>
+          <t>0507-1365-9682</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 중앙대로 104 마이우스빌딩 4층</t>
+          <t>경남 창원시 마산회원구 3·15대로 486 1층 핏불휘트니스</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/captaingym</t>
+          <t>https://blog.naver.com/pb2911</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1485,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4642a</t>
+          <t>https://talk.naver.com/ct/w4rl0g</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>691</v>
+        <v>1353</v>
       </c>
       <c r="Q11" t="n">
-        <v>251</v>
+        <v>705</v>
       </c>
       <c r="R11" t="n">
-        <v>942</v>
+        <v>2058</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,115 +1522,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1927544067</t>
+          <t>1228287028</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1927544067</t>
+          <t>https://m.place.naver.com/place/1228287028</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>핏불휘트니스 마산점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>pb2911@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1365-9682</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경남 창원시 마산회원구 3·15대로 486 1층 핏불휘트니스</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/pb2911</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4rl0g</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>1350</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>705</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2055</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1228287028</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1228287028</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/창원_헬스장.xlsx
+++ b/naver-place-crawler/results_health/창원_헬스장.xlsx
@@ -628,10 +628,10 @@
         <v>1318</v>
       </c>
       <c r="Q2" t="n">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="R2" t="n">
-        <v>2901</v>
+        <v>2902</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q3" t="n">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="R3" t="n">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         <v>833</v>
       </c>
       <c r="Q4" t="n">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="R4" t="n">
-        <v>1488</v>
+        <v>1486</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="Q5" t="n">
         <v>757</v>
       </c>
       <c r="R5" t="n">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -1020,10 +1020,10 @@
         <v>625</v>
       </c>
       <c r="Q6" t="n">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="R6" t="n">
-        <v>1134</v>
+        <v>1139</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>머슬그로우짐 중앙점</t>
+          <t>핏불휘트니스 팔용점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rldhrrl1@naver.com</t>
+          <t>pb5883@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1425-9018</t>
+          <t>0507-1339-9682</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 중앙대로 89 2층 머슬그로우짐</t>
+          <t>경남 창원시 의창구 창원대로 7 IFC빌딩 7, 8층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/musclegrowgym</t>
+          <t>https://blog.naver.com/pb5883</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcf6j8</t>
+          <t>https://talk.naver.com/ct/w44wo4</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>841</v>
+        <v>1621</v>
       </c>
       <c r="Q7" t="n">
-        <v>1341</v>
+        <v>292</v>
       </c>
       <c r="R7" t="n">
-        <v>2182</v>
+        <v>1913</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>36780621</t>
+          <t>1503804111</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36780621</t>
+          <t>https://m.place.naver.com/place/1503804111</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>빅스짐 롯데백화점 창원점</t>
+          <t>머슬그로우짐 중앙점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>bigsgymyh@naver.com</t>
+          <t>rldhrrl1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1392-4523</t>
+          <t>0507-1425-9018</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 상남로 121 8층</t>
+          <t>경남 창원시 성산구 중앙대로 89 2층 머슬그로우짐</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_lotte/</t>
+          <t>https://www.instagram.com/musclegrowgym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wa27pfo</t>
+          <t>https://talk.naver.com/ct/wcf6j8</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>165</v>
+        <v>843</v>
       </c>
       <c r="Q8" t="n">
-        <v>82</v>
+        <v>1341</v>
       </c>
       <c r="R8" t="n">
-        <v>247</v>
+        <v>2184</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2033209297</t>
+          <t>36780621</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033209297</t>
+          <t>https://m.place.naver.com/place/36780621</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>준피트니스</t>
+          <t>빅스짐 롯데백화점 창원점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>junfit26@naver.com</t>
+          <t>bigsgymyh@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1349-6855</t>
+          <t>0507-1392-4523</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경남 창원시 마산회원구 율림교로 13 4층 401호</t>
+          <t>경남 창원시 성산구 상남로 121 8층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/junfitness2026/</t>
+          <t>https://www.instagram.com/bigsgym_lotte/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wk9621e</t>
+          <t>https://talk.naver.com/ct/wa27pfo</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>165</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="R9" t="n">
-        <v>25</v>
+        <v>248</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2022834325</t>
+          <t>2033209297</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2022834325</t>
+          <t>https://m.place.naver.com/place/2033209297</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,34 +1343,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>캡틴짐 창원 상남점</t>
+          <t>준피트니스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>captaingym@naver.com</t>
+          <t>junfit26@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1352-9684</t>
+          <t>0507-1349-6855</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 중앙대로 104 마이우스빌딩 4층</t>
+          <t>경남 창원시 마산회원구 율림��로 13 4층 401호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/captaingym</t>
+          <t>https://www.instagram.com/junfitness2026/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4642a</t>
+          <t>https://talk.naver.com/ct/wk9621e</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>692</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>251</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
-        <v>943</v>
+        <v>25</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1927544067</t>
+          <t>2022834325</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1927544067</t>
+          <t>https://m.place.naver.com/place/2022834325</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1446,29 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>핏불휘트니스 마산점</t>
+          <t>캡틴짐 창원 상남점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pb2911@naver.com</t>
+          <t>captaingym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1365-9682</t>
+          <t>0507-1352-9684</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경남 창원시 마산회원구 3·15대로 486 1층 핏불휘트니스</t>
+          <t>경남 창원시 성산구 중앙대로 104 마이우스빌딩 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/pb2911</t>
+          <t>https://blog.naver.com/captaingym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4rl0g</t>
+          <t>https://talk.naver.com/ct/w4642a</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1353</v>
+        <v>694</v>
       </c>
       <c r="Q11" t="n">
-        <v>705</v>
+        <v>251</v>
       </c>
       <c r="R11" t="n">
-        <v>2058</v>
+        <v>945</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1228287028</t>
+          <t>1927544067</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1228287028</t>
+          <t>https://m.place.naver.com/place/1927544067</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/창원_헬스장.xlsx
+++ b/naver-place-crawler/results_health/창원_헬스장.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="Q5" t="n">
         <v>757</v>
       </c>
       <c r="R5" t="n">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="Q6" t="n">
         <v>514</v>
       </c>
       <c r="R6" t="n">
-        <v>1139</v>
+        <v>1144</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="Q7" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="R7" t="n">
-        <v>1913</v>
+        <v>1916</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="Q8" t="n">
         <v>1341</v>
       </c>
       <c r="R8" t="n">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1238,41 +1238,41 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>빅스짐 롯데백화점 창원점</t>
+          <t>캡틴짐 창원 상남점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>bigsgymyh@naver.com</t>
+          <t>captaingym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1392-4523</t>
+          <t>0507-1352-9684</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 상남로 121 8층</t>
+          <t>경남 창원시 성산구 중앙대로 104 마이우스빌딩 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bigsgym_lotte/</t>
+          <t>https://blog.naver.com/captaingym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wa27pfo</t>
+          <t>https://talk.naver.com/ct/w4642a</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>165</v>
+        <v>694</v>
       </c>
       <c r="Q9" t="n">
-        <v>83</v>
+        <v>251</v>
       </c>
       <c r="R9" t="n">
-        <v>248</v>
+        <v>945</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,51 +1326,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2033209297</t>
+          <t>1927544067</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2033209297</t>
+          <t>https://m.place.naver.com/place/1927544067</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>준피트니스</t>
+          <t>유즈핏 창원점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>junfit26@naver.com</t>
+          <t>uzfit2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1349-6855</t>
+          <t>0507-1365-6497</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경남 창원시 마산회원구 율림��로 13 4층 401호</t>
+          <t>경남 창원시 의창구 용동로 85 1동 4층 405호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/junfitness2026/</t>
+          <t>https://www.instagram.com/uzfit_changwon</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wk9621e</t>
+          <t>https://talk.naver.com/ct/w4q40o</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>83</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>282</v>
       </c>
       <c r="R10" t="n">
-        <v>25</v>
+        <v>365</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2022834325</t>
+          <t>1266126489</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2022834325</t>
+          <t>https://m.place.naver.com/place/1266126489</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1446,29 +1446,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>캡틴짐 창원 상남점</t>
+          <t>센트럴피지오 PT&amp;필라테스 창원점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>captaingym@naver.com</t>
+          <t>central_physio@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1352-9684</t>
+          <t>0507-1481-3514</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경남 창원시 성산구 중앙대로 104 마이우스빌딩 4층</t>
+          <t>경남 창원시 성산구 용지로133번길 5 901호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/captaingym</t>
+          <t>https://blog.naver.com/central_physio/223884089394?referrerCode=1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4642a</t>
+          <t>https://talk.naver.com/ct/w7ji4vj</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>694</v>
+        <v>95</v>
       </c>
       <c r="Q11" t="n">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="R11" t="n">
-        <v>945</v>
+        <v>318</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,17 +1522,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1927544067</t>
+          <t>2007613827</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1927544067</t>
+          <t>https://m.place.naver.com/place/2007613827</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/창원_헬스장.xlsx
+++ b/naver-place-crawler/results_health/창원_헬스장.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
